--- a/analysis_output/report_summary.xlsx
+++ b/analysis_output/report_summary.xlsx
@@ -472,7 +472,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-20T02:19:55</t>
+          <t>Generated: 2026-09-20T02:26:53</t>
         </is>
       </c>
     </row>
